--- a/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
@@ -664,7 +664,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -676,47 +676,46 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="inlineStr">
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">45
 </t>
         </is>
       </c>
+      <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -725,19 +724,25 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="n"/>
+          <t xml:space="preserve">2929
+</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -754,7 +759,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">262
@@ -781,7 +792,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -805,68 +816,84 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12620
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">316
+</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">927
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7072
+</t>
+        </is>
+      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>615</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="n"/>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -883,12 +910,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">322
@@ -897,117 +919,117 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">413
+</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">914
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="n"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">507
-</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n"/>
@@ -1026,13 +1048,13 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1074,80 +1096,65 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n"/>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1179,8 +1186,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1191,7 +1197,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1203,85 +1209,91 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">458
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">386
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1301,32 +1313,37 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n"/>
+          <t xml:space="preserve">896
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">437
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1338,89 +1355,81 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">3
+64
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
+          <t xml:space="preserve">3188
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3822
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n"/>
@@ -1439,24 +1448,25 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">235
+</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1468,93 +1478,91 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+577
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15912
-</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="n"/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1223
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1574,122 +1582,119 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2627
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1709,31 +1714,31 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">2824
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1745,83 +1750,92 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n"/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="n"/>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="n"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1841,31 +1855,32 @@
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">983
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1888,75 +1903,74 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2152
+</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1976,133 +1990,118 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">429
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1165
-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">822
-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9043
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1252
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="Z14" s="2" t="n"/>
@@ -2121,30 +2120,31 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2162,81 +2162,85 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">2429
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="n"/>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2256,124 +2260,115 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9532
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2456
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">4921
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18417
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2393,113 +2388,120 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262622
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>51</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8083
+          <t xml:space="preserve">8282
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2519,122 +2521,128 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">857
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="n"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2654,31 +2662,31 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">305
+</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2695,84 +2703,82 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9812
+          <t xml:space="preserve">9272
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="n"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">06
+</t>
         </is>
       </c>
       <c r="Z19" s="2" t="n"/>
@@ -2791,31 +2797,30 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>381</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2827,32 +2832,37 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1842
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -2864,49 +2874,42 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="n"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -2932,25 +2935,25 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2962,13 +2965,13 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2980,76 +2983,68 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">13932
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="n"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z21" s="2" t="n"/>
@@ -3068,110 +3063,120 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">3894
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12922
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -3181,12 +3186,7 @@
 </t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="n"/>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3203,42 +3203,42 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">1446
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t xml:space="preserve">32828
+</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -3249,85 +3249,83 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1999
+          <t xml:space="preserve">4978
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5360
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">0926
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4278
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">22 1
 </t>
         </is>
       </c>
@@ -3347,28 +3345,22 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">579
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">43
+</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -3383,85 +3375,84 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>486</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">282
+</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17283
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -3487,25 +3478,25 @@
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3517,7 +3508,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3528,83 +3519,94 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7922
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="Z25" s="2" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3621,31 +3623,31 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">296
+</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -3657,86 +3659,79 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5922
-</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">13922
+</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">8539
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
@@ -3755,123 +3750,127 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1291
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">913
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>537</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="Z27" s="2" t="n"/>
@@ -3890,25 +3889,25 @@
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1539
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -3920,13 +3919,13 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -3936,85 +3935,72 @@
 </t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">39086
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">64
+</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2349
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z28" s="2" t="n"/>
@@ -4033,131 +4019,128 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19584
+          <t xml:space="preserve">27511
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1902
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">4526
+</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1346
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">10426
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">3225
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="Z29" s="2" t="n"/>
@@ -4176,125 +4159,122 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26511
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">2829
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1042
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
@@ -4314,119 +4294,121 @@
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1879
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="n"/>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482
+</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4446,85 +4428,127 @@
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
       <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">248
+</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>226444</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="n"/>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -4544,121 +4568,122 @@
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">258
+</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
-</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n"/>
+          <t xml:space="preserve">7922
+</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>801</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -4675,129 +4700,134 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139326
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">582
+</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="n"/>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4814,13 +4844,13 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4832,110 +4862,104 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
-</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9282
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">94503
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2973
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">12421
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">2672
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -4955,124 +4979,121 @@
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">7857
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180902
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2852
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z36" s="2" t="n"/>
@@ -5091,125 +5112,114 @@
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">546
+</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14418
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09502
-</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="n"/>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1306
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5229,129 +5239,113 @@
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>846344</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>883384</t>
-        </is>
-      </c>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="Z38" s="2" t="n"/>
@@ -5370,117 +5364,128 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t xml:space="preserve">325
+</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43
+</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2478
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">251
 </t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">612
-</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5497,120 +5502,131 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">941
+</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1948
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">5822
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5630,126 +5646,116 @@
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="n"/>
+          <t xml:space="preserve">931
+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="n"/>
+      <c r="W41" s="2" t="n"/>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="n"/>
       <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
@@ -5763,137 +5769,121 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4262
+7
+</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">442
+</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">2429
+14
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">7
+7
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1142
+745
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19221
-</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="n"/>
+          <t xml:space="preserve">3
+6
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">3272
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Z42" s="2" t="n"/>
@@ -5912,108 +5902,105 @@
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1789
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2828
+</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77 777
+</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="inlineStr"/>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3819
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">953
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2418
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>504</t>
         </is>
       </c>
       <c r="Z43" s="2" t="n"/>
@@ -6030,98 +6017,58 @@
         </is>
       </c>
       <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13663
+          <t xml:space="preserve">3265
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21213
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="n"/>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9272
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="n"/>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6138,50 +6085,41 @@
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">184
@@ -6194,32 +6132,23 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">983
-</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">602
-</t>
-        </is>
-      </c>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="n"/>
       <c r="U45" s="2" t="inlineStr">
         <is>
@@ -6229,12 +6158,7 @@
       </c>
       <c r="V45" s="2" t="n"/>
       <c r="W45" s="2" t="n"/>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">822
-</t>
-        </is>
-      </c>
+      <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="n"/>
       <c r="Z45" s="2" t="n"/>
       <c r="AA45" t="inlineStr">
@@ -6249,98 +6173,90 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
-      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">062
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="n"/>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">8
 </t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="n"/>
+      <c r="T46" s="2" t="n"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12901
+</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1999
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="n"/>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6354,15 +6270,11 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
+      <c r="M47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+1212
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
@@ -639,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -664,7 +664,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1829
 </t>
         </is>
       </c>
@@ -676,46 +676,50 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">916
 </t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="n"/>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -724,28 +728,13 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2929
-</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
@@ -759,13 +748,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">262
@@ -774,7 +757,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
@@ -786,13 +769,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -816,88 +799,90 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">2176
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>65</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="n"/>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
@@ -913,25 +898,26 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">0170
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -940,12 +926,7 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+      <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">44
@@ -954,85 +935,95 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">2074
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="n"/>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1048,13 +1039,13 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">2105
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1096,13 +1087,13 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1203
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1110,8 +1101,7 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1120,41 +1110,51 @@
 </t>
         </is>
       </c>
-      <c r="R7" s="2" t="n"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="n"/>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -1180,13 +1180,14 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,104 +1198,99 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">458
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="n"/>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">2946
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n"/>
@@ -1313,7 +1309,7 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
@@ -1325,25 +1321,25 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">9578
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
@@ -1355,80 +1351,80 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">9492
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="n"/>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14546
+</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-64
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n"/>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11109
+</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3188
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">3186
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">19488
+</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1238
 </t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1269
+</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="n"/>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">2311
 </t>
         </is>
       </c>
@@ -1448,125 +1444,126 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">972
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>814</t>
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">912
+</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n"/>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">12822
+</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n"/>
+          <t xml:space="preserve">2162
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1588,113 +1585,114 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n"/>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2627
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">1612
+</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t xml:space="preserve">1268
+</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
@@ -1720,25 +1718,25 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2824
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -1750,92 +1748,85 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">251
 </t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="n"/>
+          <t xml:space="preserve">1612
+</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1822
 </t>
         </is>
       </c>
@@ -1861,49 +1852,33 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">983
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -1915,62 +1890,72 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="n"/>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">38
 </t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2152
-</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -1990,7 +1975,7 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2002,18 +1987,19 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">1495
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
@@ -2025,82 +2011,90 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">29234
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="n"/>
+          <t xml:space="preserve">582
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2120,116 +2114,110 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2429
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2240,7 +2228,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -2260,29 +2248,30 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">1408
+</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">1166
+</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -2294,81 +2283,89 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2456
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
+          <t>4532</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">11823
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">1266
+</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4921
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">19492
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">17088
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -2388,19 +2385,19 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2412,46 +2409,43 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">4129
+</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262622
-</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="n"/>
+          <t xml:space="preserve">1912
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -2460,48 +2454,44 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">649
+</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="n"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8282
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2521,7 +2511,7 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2532,36 +2522,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>466</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2573,70 +2563,62 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4110
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">2288
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1072
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">942
+</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -2662,31 +2644,32 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">29505
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">164
+</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2695,56 +2678,44 @@
 </t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+      <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1280
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9272
-</t>
-        </is>
-      </c>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">202
@@ -2753,31 +2724,31 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2797,31 +2768,30 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>486</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2832,90 +2802,80 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">262
+</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">219
+</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="n"/>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -2935,7 +2895,7 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -2947,104 +2907,111 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
+</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1851
-</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13932
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1191
+</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="n"/>
+          <t xml:space="preserve">882
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="Z21" s="2" t="n"/>
@@ -3063,120 +3030,116 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3894
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">939
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">2399
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">9562
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1399
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -3186,7 +3149,12 @@
 </t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1947
+</t>
+        </is>
+      </c>
       <c r="Z22" s="2" t="n"/>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3203,129 +3171,116 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446
+          <t xml:space="preserve">11441
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">2904
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32828
-</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">024644
+</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>71</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4978
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14209
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">9316
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">11210
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">93606
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">11084
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0926
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">1977
+</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">09278
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 1
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3345,22 +3300,28 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18298
+</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -3373,68 +3334,54 @@
 </t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
+          <t>13164</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">7282
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -3446,13 +3393,13 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -3484,72 +3431,68 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7922
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">11922
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1090
 </t>
         </is>
       </c>
@@ -3561,49 +3504,48 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1692
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3629,13 +3571,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1592
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -3647,10 +3589,15 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -3659,7 +3606,8 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">2188
+</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3668,70 +3616,72 @@
 </t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13922
-</t>
-        </is>
-      </c>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="n"/>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8539
+          <t xml:space="preserve">7162
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">1862
+</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
@@ -3750,25 +3700,25 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -3780,17 +3730,22 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -3799,77 +3754,68 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="n"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t xml:space="preserve">1212
+</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t xml:space="preserve">1802
+</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3895,112 +3841,121 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39086
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1687
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1190809
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">402
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">5622
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="Z28" s="2" t="n"/>
@@ -4019,127 +3974,128 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">05
+</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1892
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27511
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1958
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4526
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10426
+          <t xml:space="preserve">1394
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3225
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -4159,122 +4115,122 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">194984
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">313
+</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">2927
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2829
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11123
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1538222
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">11042
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">9284
 </t>
         </is>
       </c>
@@ -4294,121 +4250,116 @@
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1826
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4428,130 +4379,124 @@
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">14183
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">12196
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">240
+</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="n"/>
       <c r="Z32" s="2" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4568,122 +4513,123 @@
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7922
-</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="n"/>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1803
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
@@ -4700,134 +4646,123 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
+      <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">12825
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1863
+</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="Z34" s="2" t="n"/>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4844,122 +4779,123 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94503
-</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n"/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="n"/>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2973
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12421
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">8320
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2672
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -4979,121 +4915,124 @@
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">1514
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">50
+</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">918
+</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7857
-</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">90
 </t>
         </is>
       </c>
-      <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">12312
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">3852
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="Z36" s="2" t="n"/>
@@ -5112,114 +5051,127 @@
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">11615
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">87110
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">9811
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">9410
+</t>
         </is>
       </c>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">9506
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="n"/>
+          <t xml:space="preserve">1428
+</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">2413
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">1248
+</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
+          <t xml:space="preserve">3672
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5239,113 +5191,121 @@
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2515
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">941
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="n"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">410
+</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">269
+</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">12749
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z38" s="2" t="n"/>
@@ -5364,128 +5324,123 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">024516
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1791
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2478
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -5502,74 +5457,73 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">11813
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">12514
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="n"/>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1070
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">923
+</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -5578,49 +5532,49 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">2998
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">398
+</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">90
 </t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5822
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -5646,7 +5600,7 @@
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">2324
 </t>
         </is>
       </c>
@@ -5658,74 +5612,74 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">10856
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">931
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">250
 </t>
         </is>
       </c>
-      <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">10820
 </t>
         </is>
       </c>
@@ -5737,25 +5691,40 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="n"/>
-      <c r="W41" s="2" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
@@ -5772,118 +5741,122 @@
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n"/>
+          <t xml:space="preserve">11229
+</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n"/>
+          <t xml:space="preserve">11020
+</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">544
+</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2429
-14
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-745
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n"/>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2662
+</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q42" s="2" t="n"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-6
+          <t xml:space="preserve">2492
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">12221
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">9603
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3272
+          <t xml:space="preserve">102712
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">2167
+</t>
         </is>
       </c>
       <c r="Z42" s="2" t="n"/>
@@ -5900,109 +5873,28 @@
         </is>
       </c>
       <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1223
-</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1929
-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">698
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2828
-</t>
-        </is>
-      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
-      </c>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2418
-</t>
-        </is>
-      </c>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
       <c r="T43" s="2" t="n"/>
       <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
+      <c r="V43" s="2" t="n"/>
+      <c r="W43" s="2" t="n"/>
+      <c r="X43" s="2" t="n"/>
+      <c r="Y43" s="2" t="n"/>
       <c r="Z43" s="2" t="n"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6027,44 +5919,14 @@
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3265
-</t>
-        </is>
-      </c>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="n"/>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="U44" s="2" t="n"/>
       <c r="V44" s="2" t="n"/>
       <c r="W44" s="2" t="n"/>
       <c r="X44" s="2" t="n"/>
@@ -6103,63 +5965,101 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="n"/>
-      <c r="S45" s="2" t="n"/>
-      <c r="T45" s="2" t="n"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="n"/>
-      <c r="X45" s="2" t="n"/>
-      <c r="Y45" s="2" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
       <c r="Z45" s="2" t="n"/>
       <c r="AA45" t="inlineStr">
         <is>
@@ -6175,88 +6075,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 191
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
-      </c>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="n"/>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12901
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1999
-</t>
-        </is>
-      </c>
+      <c r="U46" s="2" t="n"/>
+      <c r="V46" s="2" t="n"/>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="n"/>
+          <t xml:space="preserve">92110
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198855
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165608
+</t>
+        </is>
+      </c>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6268,14 +6127,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-1212
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
@@ -624,7 +624,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">917
@@ -639,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
@@ -651,7 +651,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -661,10 +661,15 @@
 </t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -676,19 +681,19 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -700,7 +705,8 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t xml:space="preserve">306
+</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -711,13 +717,14 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t xml:space="preserve">452
+</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -732,7 +739,12 @@
 </t>
         </is>
       </c>
-      <c r="W4" s="2" t="n"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
@@ -748,16 +760,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -769,19 +781,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -799,13 +811,13 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">7146
 </t>
         </is>
       </c>
@@ -817,17 +829,19 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">994
+</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -839,7 +853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -851,36 +865,38 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -898,25 +914,25 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -926,7 +942,12 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">44
@@ -935,80 +956,85 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2074
-</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -1020,7 +1046,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1036,10 +1062,10 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2105
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -1051,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1063,7 +1089,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1798
 </t>
         </is>
       </c>
@@ -1087,21 +1113,27 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>013</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1118,22 +1150,17 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -1148,7 +1175,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1158,7 +1185,12 @@
 </t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n"/>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1171,7 +1203,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1180,13 +1212,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1204,18 +1236,20 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1233,13 +1267,14 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">080
+</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1250,7 +1285,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1262,7 +1297,8 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t xml:space="preserve">662
+</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1309,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1285,15 +1321,22 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="n"/>
+          <t xml:space="preserve">592
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1306,7 +1349,7 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1474
@@ -1315,43 +1358,43 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9578
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
@@ -1367,10 +1410,15 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1001
+</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14546
+          <t xml:space="preserve">4516
 </t>
         </is>
       </c>
@@ -1388,13 +1436,14 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11109
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1405,27 +1454,31 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n"/>
@@ -1441,7 +1494,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1450,23 +1503,28 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n"/>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -1475,11 +1533,11 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
+          <t xml:space="preserve">08604
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">185
@@ -1488,10 +1546,16 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -1500,8 +1564,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1524,13 +1587,13 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1542,25 +1605,25 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1576,7 +1639,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">290
@@ -1585,38 +1648,44 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1627,16 +1696,22 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">1183
+</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -1645,54 +1720,55 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">2398
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1709,7 +1785,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -1718,7 +1799,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -1730,13 +1811,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -1748,89 +1829,100 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672
+</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1612
-</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="n"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="n"/>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1645
+</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>7</t>
@@ -1852,45 +1944,61 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="n"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -1902,19 +2010,20 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1931,7 +2040,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1949,17 +2058,22 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="n"/>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1869
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -1972,7 +2086,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 3 3 1
+</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -1987,13 +2106,13 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1495
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2017,54 +2136,61 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29234
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -2076,7 +2202,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">2151
 </t>
         </is>
       </c>
@@ -2094,11 +2220,16 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9514
+</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>9</t>
@@ -2111,22 +2242,23 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">28919
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2137,20 +2269,26 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2161,26 +2299,31 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2192,47 +2335,52 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2095
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="n"/>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -2245,7 +2393,7 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1408
@@ -2266,12 +2414,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">481
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2283,14 +2432,20 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">9513
+</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2301,29 +2456,31 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t xml:space="preserve">94552
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11823
+          <t xml:space="preserve">11829
 </t>
         </is>
       </c>
@@ -2335,37 +2492,32 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">213142
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11585
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17088
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112746
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1005
 </t>
         </is>
       </c>
@@ -2382,88 +2534,103 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2518
+</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">233
 </t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4129
-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">649
@@ -2478,14 +2645,19 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">222 3
+</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2508,15 +2680,16 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">3089
+</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2534,18 +2707,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2557,33 +2731,39 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2594,31 +2774,31 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2641,10 +2821,10 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29505
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
@@ -2668,34 +2848,50 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
+          <t xml:space="preserve">14183
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2706,49 +2902,49 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2765,10 +2961,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">2853
+</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2785,13 +2987,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2802,33 +3005,44 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2846,36 +3060,37 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2892,10 +3107,10 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2907,19 +3122,19 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2937,26 +3152,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2968,7 +3189,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2980,19 +3201,19 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3002,15 +3223,10 @@
 </t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
+      <c r="X21" s="2" t="n"/>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3027,22 +3243,22 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3054,19 +3270,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3078,26 +3294,31 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n"/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3109,7 +3330,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3121,28 +3342,28 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9562
+          <t xml:space="preserve">8562
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">802
@@ -3151,7 +3372,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1947
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
@@ -3168,33 +3389,48 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11441
+          <t xml:space="preserve">19446
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2904
+          <t xml:space="preserve">9104
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2208
+</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
+</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -3203,25 +3439,26 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024644
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">939
+</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316
+          <t xml:space="preserve">9312
 </t>
         </is>
       </c>
@@ -3233,7 +3470,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -3245,36 +3482,37 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93606
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11084
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09278
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -3297,28 +3535,28 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18298
+          <t xml:space="preserve">8228
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1914
 </t>
         </is>
       </c>
@@ -3330,12 +3568,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10589
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">988
@@ -3344,14 +3587,20 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t xml:space="preserve">2186
+</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 312
+</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3363,19 +3612,19 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3387,22 +3636,17 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2817
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
+      <c r="X24" s="2" t="n"/>
       <c r="Y24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">25
@@ -3422,7 +3666,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">298
@@ -3431,7 +3675,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3449,13 +3693,13 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -3467,35 +3711,35 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11922
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1090
-</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -3504,7 +3748,8 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3515,37 +3760,37 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1692
+          <t xml:space="preserve">1678
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">591
 </t>
         </is>
       </c>
@@ -3562,16 +3807,16 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3595,7 +3840,8 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3606,27 +3852,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
+          <t xml:space="preserve">1926
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 18
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">7 91
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3638,19 +3894,18 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3674,7 +3929,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -3697,7 +3952,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">273
@@ -3706,7 +3966,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -3724,7 +3984,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3742,7 +4002,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3754,14 +4014,20 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n"/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3778,7 +4044,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3790,32 +4056,32 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">632
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">109
 </t>
         </is>
       </c>
-      <c r="U27" s="2" t="n"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="n"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3832,16 +4098,16 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3853,19 +4119,19 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3877,31 +4143,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n"/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190809
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -3913,13 +4185,14 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t xml:space="preserve">2740
+</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3930,31 +4203,31 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5622
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3971,7 +4244,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">301
@@ -3980,68 +4253,72 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1918
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1892
-</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1958
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="n"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4071,31 +4348,31 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1394
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4112,10 +4389,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194984
+          <t xml:space="preserve">19484
 </t>
         </is>
       </c>
@@ -4145,92 +4427,98 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2927
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">9207
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11123
-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="n"/>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538222
+          <t xml:space="preserve">33222
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">10881
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11042
+          <t xml:space="preserve">11841
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9284
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -4247,16 +4535,16 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">2397
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4268,7 +4556,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -4280,23 +4568,35 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -4305,61 +4605,61 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">773
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4376,33 +4676,35 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1118
+</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4413,7 +4715,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4435,10 +4737,15 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12196
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4456,7 +4763,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4468,31 +4775,31 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">2881
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">4155
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -4510,7 +4817,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">326
@@ -4519,19 +4831,19 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4543,33 +4855,43 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -4599,37 +4921,37 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">1658
 </t>
         </is>
       </c>
@@ -4646,10 +4968,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -4661,7 +4988,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2418
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4679,19 +5006,19 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -4701,18 +5028,33 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1511
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12825
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -4730,13 +5072,14 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4747,19 +5090,19 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4779,31 +5122,30 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4831,11 +5173,21 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="n"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9942
 </t>
         </is>
       </c>
@@ -4865,19 +5217,19 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8320
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -4889,13 +5241,13 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
@@ -4912,10 +5264,10 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">336
 </t>
         </is>
       </c>
@@ -4939,19 +5291,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1514
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -4967,29 +5319,34 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5007,7 +5364,7 @@
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5025,13 +5382,13 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3852
+          <t xml:space="preserve">557
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5048,7 +5405,7 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">11615
@@ -5057,7 +5414,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -5069,46 +5426,52 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87110
+          <t xml:space="preserve">8180
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">0117
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n"/>
+          <t xml:space="preserve">7210
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">9506
@@ -5117,7 +5480,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -5129,34 +5492,34 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1206
+</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1110
 </t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2413
-</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1009
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1299
@@ -5165,13 +5528,13 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3672
+          <t xml:space="preserve">36722
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">5372
 </t>
         </is>
       </c>
@@ -5188,10 +5551,11 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5202,7 +5566,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515
+          <t xml:space="preserve">25246
 </t>
         </is>
       </c>
@@ -5214,44 +5578,50 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n"/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5269,25 +5639,25 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12749
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5305,7 +5675,8 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="2" t="n"/>
@@ -5324,72 +5695,75 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024516
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1791
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5400,7 +5774,8 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t xml:space="preserve">1426
+</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -5411,13 +5786,14 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -5434,16 +5810,11 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="n"/>
       <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5457,22 +5828,22 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11813
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12514
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5484,7 +5855,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5496,31 +5867,32 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1070
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5532,31 +5904,31 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2998
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2608
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">1926
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -5568,13 +5940,13 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">2518
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -5597,22 +5969,22 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324
+          <t xml:space="preserve">9218
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10856
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5624,44 +5996,44 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">2049
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -5673,25 +6045,25 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10820
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5709,13 +6081,13 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5738,127 +6110,114 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11229
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11020
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">544
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">19502
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="n"/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="n"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12221
-</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9603
-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102712
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="n"/>
+      <c r="W42" s="2" t="n"/>
+      <c r="X42" s="2" t="n"/>
+      <c r="Y42" s="2" t="n"/>
       <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
@@ -5872,7 +6231,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
@@ -5908,7 +6272,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -5947,116 +6316,128 @@
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">2412
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">5097
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">8187
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">9663
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">02712
+</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -6073,46 +6454,121 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">937
+</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="n"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92110
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198855
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165608
+          <t xml:space="preserve">12111011
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -639,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -651,7 +651,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -687,13 +687,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -717,14 +716,13 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
-</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -735,7 +733,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -760,7 +758,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">252
@@ -775,7 +778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -787,25 +790,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -817,19 +819,19 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">994
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -853,7 +855,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -877,7 +879,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -914,133 +916,133 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">272
 </t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">975
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1132,13 +1134,13 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">4201
 </t>
         </is>
       </c>
@@ -1150,17 +1152,22 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -1175,7 +1182,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -1187,7 +1194,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1203,7 +1210,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1218,7 +1230,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1236,13 +1248,13 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1297,7 +1309,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1309,7 +1321,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1327,13 +1339,13 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1358,7 +1370,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
@@ -1370,7 +1382,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
@@ -1388,28 +1400,28 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">9441
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">926
 </t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1001
@@ -1418,8 +1430,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
-</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1442,7 +1453,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -1454,13 +1465,13 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1478,7 +1489,8 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n"/>
@@ -1494,7 +1506,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1515,13 +1532,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1916
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1533,11 +1550,16 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08604
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">185
@@ -1552,7 +1574,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1593,7 +1615,7 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1623,7 +1645,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -1666,13 +1688,13 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -1684,14 +1706,13 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1702,16 +1723,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -1726,31 +1742,31 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2398
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1762,7 +1778,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1787,7 +1803,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1799,7 +1815,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1811,13 +1827,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -1835,7 +1851,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
@@ -1853,7 +1869,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1871,7 +1887,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -1883,19 +1899,19 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1907,19 +1923,25 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="n"/>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">832
+</t>
+        </is>
+      </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -1950,7 +1972,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1962,7 +1984,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -1974,7 +1996,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1998,7 +2020,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2016,7 +2038,7 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -2040,7 +2062,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -2070,7 +2092,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1869
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2086,12 +2108,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 3 3 1
-</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2106,7 +2123,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2118,7 +2135,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -2148,19 +2165,14 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -2172,7 +2184,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -2184,13 +2196,13 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -2202,7 +2214,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
@@ -2220,13 +2232,13 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">7172
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9514
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2242,16 +2254,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28919
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2275,19 +2292,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2299,25 +2316,25 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
@@ -2335,7 +2352,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -2359,7 +2376,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2377,7 +2394,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2396,19 +2413,18 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">19404
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -2420,7 +2436,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">015
 </t>
         </is>
       </c>
@@ -2432,13 +2448,13 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -2462,7 +2478,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94552
+          <t xml:space="preserve">4532
 </t>
         </is>
       </c>
@@ -2474,13 +2490,13 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11829
+          <t xml:space="preserve">11273
 </t>
         </is>
       </c>
@@ -2492,32 +2508,32 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213142
+          <t xml:space="preserve">0182
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11585
+          <t xml:space="preserve">9848
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112746
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1005
+          <t xml:space="preserve">100646
 </t>
         </is>
       </c>
@@ -2534,15 +2550,10 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2554,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2578,7 +2589,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -2591,16 +2602,11 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">91
@@ -2609,7 +2615,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2621,19 +2627,19 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2353
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -2645,7 +2651,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222 3
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2683,37 +2689,36 @@
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3089
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2731,13 +2736,13 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2756,8 +2761,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2774,13 +2778,13 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2792,7 +2796,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2821,10 +2825,15 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -2848,7 +2857,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>469</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2871,7 +2880,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2908,19 +2917,19 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2961,21 +2970,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3023,11 +3027,16 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">902
@@ -3054,25 +3063,25 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -3084,7 +3093,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3110,8 +3119,7 @@
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3128,22 +3136,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -3152,7 +3160,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -3183,13 +3191,13 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3201,13 +3209,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -3246,8 +3254,7 @@
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3258,34 +3265,34 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2328
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">232
 </t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -3300,13 +3307,13 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3342,7 +3349,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8562
+          <t xml:space="preserve">89562
 </t>
         </is>
       </c>
@@ -3389,58 +3396,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19446
+          <t xml:space="preserve">1944
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3451,23 +3451,22 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n"/>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9312
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1210
@@ -3476,7 +3475,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
@@ -3488,7 +3487,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">3602
 </t>
         </is>
       </c>
@@ -3506,19 +3505,19 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">0949278
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3538,7 +3537,7 @@
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -3550,13 +3549,13 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -3568,20 +3567,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10589
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -3591,16 +3589,16 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 312
+          <t xml:space="preserve">5812
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3612,19 +3610,19 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">28239
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
@@ -3636,7 +3634,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2817
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -3666,11 +3664,15 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3681,56 +3683,50 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3760,8 +3756,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3772,25 +3767,25 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1678
+          <t xml:space="preserve">8713
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3810,7 +3805,7 @@
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2986
 </t>
         </is>
       </c>
@@ -3834,7 +3829,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3852,37 +3847,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 91
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3894,18 +3884,19 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
@@ -3952,12 +3943,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">273
@@ -3966,7 +3952,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -3984,7 +3970,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -3996,13 +3982,13 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4014,19 +4000,19 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">8118
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4038,13 +4024,13 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -4062,13 +4048,13 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -4081,7 +4067,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4101,13 +4087,13 @@
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4119,7 +4105,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4131,7 +4117,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -4143,37 +4129,36 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">12724
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4191,7 +4176,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2740
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
@@ -4203,32 +4188,31 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="Z28" s="2" t="n"/>
@@ -4265,7 +4249,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4277,7 +4261,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4301,19 +4285,14 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>407</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4336,7 +4315,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4360,7 +4339,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4372,7 +4351,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4389,27 +4368,22 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19484
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -4439,44 +4413,43 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9207
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
@@ -4488,37 +4461,36 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10881
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11841
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -4538,19 +4510,19 @@
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -4581,7 +4553,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -4593,7 +4565,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4605,7 +4577,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4617,7 +4589,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -4629,13 +4601,13 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">641
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -4659,7 +4631,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -4676,11 +4648,10 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4691,7 +4662,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -4703,19 +4674,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4727,25 +4698,20 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
@@ -4763,7 +4729,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4775,13 +4741,13 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -4799,7 +4765,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4817,21 +4783,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4855,7 +4815,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4873,28 +4833,23 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">9198
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -4909,7 +4864,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -4921,7 +4876,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4933,13 +4888,13 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4951,7 +4906,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -4968,12 +4923,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">321
@@ -4982,7 +4932,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -5012,13 +4962,13 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5030,19 +4980,19 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1919
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5054,7 +5004,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5072,13 +5022,13 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5102,7 +5052,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5122,19 +5072,20 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -5145,7 +5096,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5169,25 +5120,25 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9942
+          <t xml:space="preserve">1724
 </t>
         </is>
       </c>
@@ -5217,7 +5168,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
@@ -5229,7 +5180,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -5247,7 +5198,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5264,17 +5215,16 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5285,7 +5235,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5297,13 +5247,13 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5319,25 +5269,24 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1212
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4706
-</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">312
@@ -5346,7 +5295,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -5358,7 +5307,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5382,13 +5331,13 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -5408,13 +5357,13 @@
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11615
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -5426,61 +5375,61 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8180
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0117
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">9499
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7210
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9506
+          <t xml:space="preserve">9502
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5492,13 +5441,13 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">12304
 </t>
         </is>
       </c>
@@ -5510,13 +5459,13 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5528,13 +5477,13 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36722
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5551,7 +5500,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">123
@@ -5566,19 +5515,19 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25246
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5590,32 +5539,31 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -5639,7 +5587,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -5657,7 +5605,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -5675,7 +5623,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5701,31 +5649,31 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5737,26 +5685,26 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">7960
 </t>
         </is>
       </c>
@@ -5774,7 +5722,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -5786,19 +5734,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -5810,7 +5758,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5843,7 +5791,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5855,7 +5803,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5867,13 +5815,13 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -5904,31 +5852,31 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2822
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -5940,13 +5888,13 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5969,37 +5917,37 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">179 0
+</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">29
@@ -6008,7 +5956,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -6020,29 +5968,24 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2049
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">992
+</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">24
@@ -6063,7 +6006,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6075,8 +6018,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -6087,7 +6029,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
@@ -6110,7 +6052,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">324
@@ -6119,25 +6061,25 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6149,7 +6091,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6161,22 +6103,17 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1984
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19502
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -6203,14 +6140,19 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="n"/>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 14
+</t>
+        </is>
+      </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6328,13 +6270,13 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6346,25 +6288,23 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>056</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1411
 </t>
         </is>
       </c>
@@ -6376,13 +6316,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -6407,37 +6346,37 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5097
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9663
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02712
+          <t xml:space="preserve">2212
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6475,7 +6414,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6493,20 +6432,25 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6518,7 +6462,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6562,13 +6506,13 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111011
+          <t xml:space="preserve">872085
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -687,12 +687,13 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -716,13 +717,14 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -733,7 +735,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -758,15 +760,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -778,19 +775,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -802,33 +799,34 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -861,7 +859,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
@@ -873,7 +871,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -891,7 +889,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -922,13 +920,13 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
@@ -952,7 +950,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -974,21 +972,16 @@
 </t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">9212
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1012,13 +1005,13 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">3906
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1030,25 +1023,25 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1067,7 +1060,7 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">2305
 </t>
         </is>
       </c>
@@ -1079,7 +1072,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -1091,7 +1084,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1798
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1109,7 +1102,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1121,14 +1114,18 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n"/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1140,7 +1137,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4201
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -1158,7 +1155,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1188,13 +1185,13 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -1210,12 +1207,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1230,8 +1222,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1248,7 +1239,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1279,13 +1270,13 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">7912
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1309,7 +1300,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
@@ -1321,7 +1312,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1339,13 +1330,13 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -1364,14 +1355,13 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">1479
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1382,14 +1372,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1400,37 +1389,38 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">39726
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t xml:space="preserve">4512
+</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1447,13 +1437,13 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -1483,17 +1473,21 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3826
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="Z9" s="2" t="n"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1506,12 +1500,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1520,7 +1509,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1532,13 +1521,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1550,13 +1539,13 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1574,19 +1563,20 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1609,7 +1599,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1639,13 +1629,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1664,7 +1654,7 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -1676,61 +1666,51 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916
+</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1742,7 +1722,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1754,8 +1734,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1766,13 +1745,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -1788,7 +1766,12 @@
 </t>
         </is>
       </c>
-      <c r="Z11" s="2" t="n"/>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1801,12 +1784,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -1827,19 +1805,19 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">9 841
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1851,13 +1829,13 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1869,7 +1847,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1881,13 +1859,13 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1905,13 +1883,13 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -1923,25 +1901,25 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1957,7 +1935,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1966,7 +1944,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1978,7 +1956,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
@@ -1996,7 +1974,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2008,25 +1986,25 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2062,7 +2040,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -2092,7 +2070,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2108,7 +2086,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2135,7 +2118,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2147,13 +2130,13 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2165,11 +2148,16 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -2196,13 +2184,13 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
@@ -2214,7 +2202,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -2232,7 +2220,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7172
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -2254,15 +2242,10 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -2274,7 +2257,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2935
 </t>
         </is>
       </c>
@@ -2286,13 +2269,13 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">0179
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -2304,8 +2287,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2322,19 +2304,19 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2352,7 +2334,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2370,7 +2352,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -2394,7 +2376,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -2413,54 +2395,49 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19404
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1123
+</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -2472,31 +2449,31 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532
+          <t xml:space="preserve">8532
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11273
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -2508,36 +2485,45 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182
-</t>
+          <t>382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9848
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="n"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100646
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="n"/>
+          <t xml:space="preserve">9708
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2553,25 +2539,24 @@
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -2589,27 +2574,32 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -2621,7 +2611,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2633,25 +2623,25 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2669,11 +2659,16 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="Z17" s="2" t="n"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2689,49 +2684,45 @@
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2746,22 +2737,27 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0 2
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>892</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2778,13 +2774,13 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">542
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2802,17 +2798,21 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="Z18" s="2" t="n"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2827,13 +2827,13 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2857,12 +2857,13 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2886,11 +2887,16 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -2929,7 +2935,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2941,7 +2947,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2953,11 +2959,16 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="Z19" s="2" t="n"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2970,16 +2981,21 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2991,7 +3007,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">0596
 </t>
         </is>
       </c>
@@ -3015,31 +3031,26 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
@@ -3063,13 +3074,13 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -3081,7 +3092,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3093,7 +3104,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
@@ -3103,7 +3114,11 @@
 </t>
         </is>
       </c>
-      <c r="Z20" s="2" t="n"/>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3116,10 +3131,16 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3130,7 +3151,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3142,7 +3163,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3160,7 +3181,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3191,13 +3212,13 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3209,36 +3230,46 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="X21" s="2" t="n"/>
       <c r="Y21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">903
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3251,21 +3282,27 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3289,7 +3326,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3301,25 +3338,25 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">9912
 </t>
         </is>
       </c>
@@ -3331,13 +3368,13 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3349,7 +3386,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89562
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -3361,29 +3398,34 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">947
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="n"/>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3399,7 +3441,7 @@
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19426
 </t>
         </is>
       </c>
@@ -3411,36 +3453,37 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3451,19 +3494,20 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">19529
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t xml:space="preserve">9512
+</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
@@ -3475,53 +3519,58 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3602
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">377
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0949278
+          <t xml:space="preserve">1987
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="n"/>
+          <t xml:space="preserve">94256
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3534,7 +3583,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">285
@@ -3567,38 +3621,48 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5812
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3610,19 +3674,19 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -3634,7 +3698,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">8217
 </t>
         </is>
       </c>
@@ -3644,14 +3708,24 @@
 </t>
         </is>
       </c>
-      <c r="X24" s="2" t="n"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="Z24" s="2" t="n"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3664,88 +3738,91 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4441</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3756,12 +3833,13 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -3773,23 +3851,22 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8713
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="n"/>
+          <t xml:space="preserve">693
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3802,16 +3879,21 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2986
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -3823,7 +3905,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -3847,26 +3929,31 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19896
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -3884,13 +3971,13 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3908,29 +3995,34 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="n"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -3964,7 +4056,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -3976,19 +4068,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4000,19 +4092,19 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">9222
 </t>
         </is>
       </c>
@@ -4024,13 +4116,13 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4048,30 +4140,40 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="W27" s="2" t="n"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="n"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -4087,13 +4189,13 @@
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">2327
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4105,7 +4207,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4129,60 +4231,61 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12724
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">402
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4194,28 +4297,34 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>856</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="n"/>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4243,31 +4352,31 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4283,21 +4392,22 @@
 </t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4315,7 +4425,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4333,29 +4443,34 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="n"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -4371,25 +4486,25 @@
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">14984
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1896
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4407,32 +4522,32 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">2925
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">961
+          <t xml:space="preserve">3921
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4449,7 +4564,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4473,28 +4588,33 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t xml:space="preserve">3122
+</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="Z30" s="2" t="n"/>
+          <t xml:space="preserve">524
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4516,7 +4636,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4528,13 +4648,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4546,14 +4666,14 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4565,7 +4685,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -4583,25 +4703,25 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">641
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -4613,29 +4733,34 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">773
+          <t xml:space="preserve">7478
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="n"/>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4648,22 +4773,26 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">12328
+</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4674,19 +4803,18 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4696,35 +4824,34 @@
 </t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -4741,7 +4868,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -4753,7 +4880,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4765,11 +4892,15 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="n"/>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4783,10 +4914,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">926
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4833,20 +4970,20 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4864,7 +5001,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4876,41 +5013,46 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">803
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">803
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="n"/>
       <c r="AA33" t="inlineStr">
         <is>
           <t>22</t>
@@ -4932,13 +5074,13 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -4950,7 +5092,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -4968,7 +5110,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4980,7 +5122,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4992,19 +5134,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5022,13 +5164,13 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5052,11 +5194,16 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="n"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -5069,7 +5216,12 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -5120,25 +5272,20 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1724
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5150,7 +5297,7 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5168,7 +5315,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -5202,7 +5349,12 @@
 </t>
         </is>
       </c>
-      <c r="Z35" s="2" t="n"/>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5215,16 +5367,17 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">9336
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5253,7 +5406,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5265,25 +5418,31 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5295,7 +5454,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2350
 </t>
         </is>
       </c>
@@ -5307,13 +5466,13 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -5331,13 +5490,13 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -5363,7 +5522,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">19295
 </t>
         </is>
       </c>
@@ -5375,14 +5534,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -5393,7 +5551,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5405,31 +5563,31 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">9511
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9502
+          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5441,43 +5599,43 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12304
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">73672
 </t>
         </is>
       </c>
@@ -5487,7 +5645,12 @@
 </t>
         </is>
       </c>
-      <c r="Z37" s="2" t="n"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2473
+</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5500,7 +5663,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">123
@@ -5515,7 +5678,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5539,31 +5702,32 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
@@ -5581,53 +5745,58 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">7235
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">149
 </t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="n"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5643,37 +5812,35 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5685,26 +5852,26 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1490
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
@@ -5722,48 +5889,57 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="n"/>
-      <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5776,7 +5952,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">325
@@ -5791,7 +5972,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5803,7 +5984,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5815,13 +5996,13 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5833,11 +6014,16 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -5852,13 +6038,13 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2822
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5870,19 +6056,19 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -5894,7 +6080,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5904,7 +6090,12 @@
 </t>
         </is>
       </c>
-      <c r="Z40" s="2" t="n"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8262
+</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>27</t>
@@ -5917,16 +6108,16 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179 0
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5944,14 +6135,13 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5962,13 +6152,13 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2091
 </t>
         </is>
       </c>
@@ -5978,17 +6168,22 @@
 </t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -6006,30 +6201,31 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6039,7 +6235,12 @@
 </t>
         </is>
       </c>
-      <c r="Z41" s="2" t="n"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6053,33 +6254,28 @@
         </is>
       </c>
       <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">324
 </t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6091,73 +6287,88 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1728
+</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">86
 </t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 14
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="n"/>
-      <c r="W42" s="2" t="n"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="X42" s="2" t="n"/>
       <c r="Y42" s="2" t="n"/>
       <c r="Z42" s="2" t="n"/>
@@ -6270,58 +6481,55 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>056</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">23662
 </t>
         </is>
       </c>
@@ -6331,10 +6539,15 @@
 </t>
         </is>
       </c>
-      <c r="Q45" s="2" t="n"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1069
+</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">1027
 </t>
         </is>
       </c>
@@ -6346,19 +6559,19 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">8927
 </t>
         </is>
       </c>
@@ -6370,17 +6583,22 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
+          <t xml:space="preserve">193272
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6396,28 +6614,28 @@
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
 </t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -6426,37 +6644,37 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6468,55 +6686,65 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">229
 </t>
         </is>
       </c>
-      <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">602
 </t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">823
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872085
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="n"/>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 9929
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
@@ -627,122 +627,102 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="2" t="n"/>
@@ -763,140 +743,117 @@
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -914,135 +871,113 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1060,62 +995,52 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,74 +1050,62 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1210,14 +1123,12 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1227,117 +1138,98 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1355,8 +1247,7 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1366,14 +1257,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1383,92 +1272,77 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39726
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
-</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
-</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>488</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1478,14 +1352,12 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
-</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1503,140 +1375,117 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,33 +1503,28 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1692,44 +1536,37 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1739,8 +1576,7 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1750,26 +1586,22 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,140 +1619,117 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 841
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">086
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,140 +1747,117 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2088,146 +1874,122 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2245,44 +2007,37 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2935
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2292,92 +2047,77 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2395,20 +2135,17 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2418,69 +2155,58 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2490,38 +2216,32 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9708
-</t>
+          <t>088</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2536,17 +2256,19 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2556,117 +2278,98 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2704,20 +2407,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2727,32 +2427,27 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 2
-</t>
+          <t>0 2</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2762,38 +2457,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">542
-</t>
+          <t>542</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -2803,14 +2492,12 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2827,146 +2514,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2983,135 +2646,113 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0596
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -3133,141 +2774,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3284,146 +2906,122 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3441,20 +3039,17 @@
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19426
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3464,111 +3059,93 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>838</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19529
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9512
-</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
-</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1987
-</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94256
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3585,44 +3162,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3632,98 +3202,82 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
-</t>
+          <t>99919991</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3741,20 +3295,17 @@
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3764,14 +3315,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3781,38 +3330,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3827,26 +3370,22 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3856,14 +3395,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">693
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -3881,146 +3418,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19896
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4038,140 +3551,117 @@
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4189,140 +3679,117 @@
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>402</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4340,135 +3807,113 @@
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4486,44 +3931,37 @@
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14984
-</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>588</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4533,81 +3971,68 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3921
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3122
-</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4630,135 +4055,113 @@
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7478
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4775,14 +4178,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12328
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4797,14 +4198,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4814,39 +4213,33 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4856,38 +4249,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>358</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
@@ -4897,8 +4284,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="Z32" s="2" t="n"/>
@@ -4916,141 +4302,118 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5065,143 +4428,124 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5218,141 +4562,118 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5370,134 +4691,112 @@
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9336
-</t>
+          <t>936</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Z36" s="2" t="n"/>
@@ -5516,26 +4815,22 @@
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
-</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19295
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5545,110 +4840,92 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9499
-</t>
+          <t>491</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9511
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1502
-</t>
+          <t>502</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
-</t>
+          <t>703</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
-</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73672
-</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2473
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5666,135 +4943,117 @@
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5812,8 +5071,7 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -5823,8 +5081,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5834,93 +5091,78 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241 7</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
@@ -5930,14 +5172,12 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5954,146 +5194,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
-</t>
+          <t>472</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8262
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6111,32 +5327,27 @@
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -6146,99 +5357,83 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6257,116 +5452,97 @@
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="X42" s="2" t="n"/>
@@ -6386,8 +5562,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D43" s="2" t="n"/>
@@ -6427,8 +5602,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -6469,26 +5643,22 @@
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -6498,105 +5668,88 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23662
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
-</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2412
-</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
-</t>
+          <t>387</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8927
-</t>
+          <t>857</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193272
-</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6614,135 +5767,113 @@
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 9929
-</t>
+          <t>0 22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -818,27 +818,27 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>212</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>196</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2 81</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 1 01</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>815</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>173</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>412</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2293,23 +2293,23 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>221</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>101</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>289</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>219</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -3039,7 +3039,7 @@
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
@@ -3110,17 +3110,17 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>347</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>99919991</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>856</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3468,17 +3468,17 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>293</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>000</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>278</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3976,13 +3976,13 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>921</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>451</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>876</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>903</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>482</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>262</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>803</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N35" s="2" t="n"/>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>254</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>86</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>442</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4943,7 +4943,7 @@
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>186</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5116,13 +5116,13 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>241 7</t>
+          <t>241 0</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>298</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>196</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>269</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5497,52 +5497,52 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X42" s="2" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>963</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5767,7 +5767,7 @@
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>99</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -5817,42 +5817,42 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>223</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5870,10 +5870,14 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>2 1</t>
+        </is>
+      </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>0 22</t>
+          <t>00 2989</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Midpoint_Excel_with_OCR_Results.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>104</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1674,17 +1674,17 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>905</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>67</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0 1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>919</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>353</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>109</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>114</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2559,22 +2559,22 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0 01</t>
+          <t>0 0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>88</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3039,7 +3039,7 @@
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>577</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>812</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>673</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -3418,67 +3418,67 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>918</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3493,17 +3493,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>08</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>63</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3976,13 +3976,13 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,17 +4017,17 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>263</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>803</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>78</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>290</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4480,17 +4480,17 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>09</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4860,17 +4860,17 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4978,37 +4978,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>886</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5122,7 +5122,7 @@
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>95</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5244,17 +5244,17 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>869</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="2" t="n"/>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5683,18 +5683,18 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>311</t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>241</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -5724,22 +5724,22 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>327</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5792,42 +5792,42 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5870,14 +5870,10 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>2 1</t>
-        </is>
-      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>00 2989</t>
+          <t>0 2989</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
